--- a/artfynd/A 20233-2026 artfynd.xlsx
+++ b/artfynd/A 20233-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91265887</v>
+        <v>91265860</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>104628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>572726</v>
+        <v>572687</v>
       </c>
       <c r="R2" t="n">
-        <v>6765478</v>
+        <v>6765588</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,12 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Strand, åstrand vid skogså, fors eller ström, i björkskog</t>
+          <t>Strand, åstrand kring sidofåra av skogså, översilat vid     högvatten</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>Gst Fyndnr 303866N</t>
+          <t>Gst Fyndnr 303892N</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -779,6 +779,228 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91265877</v>
+      </c>
+      <c r="B3" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bredsiljeån, Långrännströmmen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>572724</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6765528</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Strand, åstrand till skogså, på björk-granbevuxen låg ö     omfluten av vatten åtm vid högvatten, rundstenigt, översilat</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 303876N</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91265887</v>
+      </c>
+      <c r="B4" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bredsiljeån, Långrännströmmen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>572726</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6765478</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2008-06-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Strand, åstrand vid skogså, fors eller ström, i björkskog</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 303866N</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Peter Ståhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
